--- a/tools/exemplos/(BASE) - Metas Polybalas - Totais.xlsx
+++ b/tools/exemplos/(BASE) - Metas Polybalas - Totais.xlsx
@@ -451,7 +451,7 @@
         <v>535000</v>
       </c>
       <c r="C2" t="n">
-        <v>832</v>
+        <v>806</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>618000</v>
       </c>
       <c r="C3" t="n">
-        <v>1106</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         <v>900000</v>
       </c>
       <c r="C4" t="n">
-        <v>745</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>615000</v>
       </c>
       <c r="C5" t="n">
-        <v>1279</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
@@ -503,7 +503,7 @@
         <v>430000</v>
       </c>
       <c r="C6" t="n">
-        <v>955</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         <v>417000</v>
       </c>
       <c r="C7" t="n">
-        <v>984</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8">
@@ -529,7 +529,7 @@
         <v>55000</v>
       </c>
       <c r="C8" t="n">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         <v>30000</v>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10">
@@ -555,7 +555,7 @@
         <v>3600000</v>
       </c>
       <c r="C10" t="n">
-        <v>1705</v>
+        <v>1934</v>
       </c>
     </row>
   </sheetData>

--- a/tools/exemplos/(BASE) - Metas Polybalas - Totais.xlsx
+++ b/tools/exemplos/(BASE) - Metas Polybalas - Totais.xlsx
@@ -451,7 +451,7 @@
         <v>535000</v>
       </c>
       <c r="C2" t="n">
-        <v>806</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>618000</v>
       </c>
       <c r="C3" t="n">
-        <v>1075</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         <v>900000</v>
       </c>
       <c r="C4" t="n">
-        <v>710</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>615000</v>
       </c>
       <c r="C5" t="n">
-        <v>1274</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6">
@@ -503,7 +503,7 @@
         <v>430000</v>
       </c>
       <c r="C6" t="n">
-        <v>927</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         <v>417000</v>
       </c>
       <c r="C7" t="n">
-        <v>962</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -529,7 +529,7 @@
         <v>55000</v>
       </c>
       <c r="C8" t="n">
-        <v>679</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         <v>30000</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10">
@@ -555,7 +555,7 @@
         <v>3600000</v>
       </c>
       <c r="C10" t="n">
-        <v>1934</v>
+        <v>2367</v>
       </c>
     </row>
   </sheetData>
